--- a/Hershey_failed_to_download.xlsx
+++ b/Hershey_failed_to_download.xlsx
@@ -437,7 +437,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15281666638</v>
+        <v>15281656269</v>
       </c>
     </row>
     <row r="3">
@@ -447,22 +447,22 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>15281704504</v>
+        <v>15281666637</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>15281656271</v>
+        <v>15281666638</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15281656269</v>
+        <v>15281704504</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>15281666637</v>
+        <v>15281656271</v>
       </c>
     </row>
   </sheetData>
